--- a/resultados_turnos.xlsx
+++ b/resultados_turnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
   <si>
     <t>Día 1</t>
   </si>
@@ -37,46 +37,40 @@
     <t>Turno</t>
   </si>
   <si>
-    <t>diurno (08:00-20:00)</t>
-  </si>
-  <si>
-    <t>nocturno (20:00-08:00)</t>
-  </si>
-  <si>
-    <t>Reten1 / Reten5 / Reten6 / Reten9 / Reten17 / Reten21 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten9 / Reten10 / Reten15 / Reten16 / Reten18 / Reten19 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten5 / Reten6 / Reten9 / Reten15 / Reten17 / Reten18 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten1 / Reten6 / Reten10 / Reten12 / Reten18 / Reten21 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten2 / Reten7 / Reten8 / Reten12 / Reten20 / Reten21 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten7 / Reten11 / Reten15 / Reten16 / Reten17 / Reten21 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten6 / Reten10 / Reten11 / Reten13 / Reten15 / Reten21 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten5 / Reten7 / Reten16 / Reten17 / Reten19 / Reten22 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten8 / Reten11 / Reten12 / Reten14 / Reten17 / Reten21 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten10 / Reten11 / Reten15 / Reten18 / Reten19 / Reten20 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten4 / Reten9 / Reten12 / Reten13 / Reten15 / Reten18 / Conductor1 / Conductor2</t>
-  </si>
-  <si>
-    <t>Reten2 / Reten4 / Reten7 / Reten11 / Reten13 / Reten19 / Conductor1 / Conductor2</t>
+    <t>diurno</t>
+  </si>
+  <si>
+    <t>nocturno</t>
+  </si>
+  <si>
+    <t>reten_4 / reten_5 / reten_7 / reten_10 / reten_11 / reten_12 / reten_14 / conductor_1</t>
+  </si>
+  <si>
+    <t>reten_1 / reten_2 / reten_3 / reten_9 / reten_17 / reten_19 / reten_22 / conductor_3</t>
+  </si>
+  <si>
+    <t>reten_4 / reten_5 / reten_7 / reten_10 / reten_13 / reten_15 / reten_20 / conductor_2</t>
+  </si>
+  <si>
+    <t>reten_2 / reten_6 / reten_8 / reten_9 / reten_17 / reten_18 / reten_21 / conductor_4</t>
+  </si>
+  <si>
+    <t>reten_1 / reten_3 / reten_13 / reten_15 / reten_19 / reten_20 / reten_22 / conductor_3</t>
+  </si>
+  <si>
+    <t>reten_8 / reten_11 / reten_12 / reten_14 / reten_16 / reten_18 / reten_21 / conductor_4</t>
+  </si>
+  <si>
+    <t>reten_5 / reten_7 / reten_10 / reten_11 / reten_12 / reten_14 / reten_16 / conductor_4</t>
+  </si>
+  <si>
+    <t>reten_2 / reten_6 / reten_8 / reten_9 / reten_17 / reten_18 / reten_21 / conductor_3</t>
+  </si>
+  <si>
+    <t>reten_6 / reten_8 / reten_11 / reten_12 / reten_14 / reten_16 / reten_18 / conductor_4</t>
+  </si>
+  <si>
+    <t>reten_1 / reten_4 / reten_13 / reten_15 / reten_19 / reten_20 / reten_22 / conductor_1</t>
   </si>
 </sst>
 </file>
@@ -485,13 +479,13 @@
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -508,13 +502,13 @@
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/resultados_turnos.xlsx
+++ b/resultados_turnos.xlsx
@@ -37,40 +37,40 @@
     <t>Turno</t>
   </si>
   <si>
-    <t>diurno</t>
-  </si>
-  <si>
-    <t>nocturno</t>
-  </si>
-  <si>
-    <t>reten_4 / reten_5 / reten_7 / reten_10 / reten_11 / reten_12 / reten_14 / conductor_1</t>
-  </si>
-  <si>
-    <t>reten_1 / reten_2 / reten_3 / reten_9 / reten_17 / reten_19 / reten_22 / conductor_3</t>
-  </si>
-  <si>
-    <t>reten_4 / reten_5 / reten_7 / reten_10 / reten_13 / reten_15 / reten_20 / conductor_2</t>
-  </si>
-  <si>
-    <t>reten_2 / reten_6 / reten_8 / reten_9 / reten_17 / reten_18 / reten_21 / conductor_4</t>
-  </si>
-  <si>
-    <t>reten_1 / reten_3 / reten_13 / reten_15 / reten_19 / reten_20 / reten_22 / conductor_3</t>
-  </si>
-  <si>
-    <t>reten_8 / reten_11 / reten_12 / reten_14 / reten_16 / reten_18 / reten_21 / conductor_4</t>
-  </si>
-  <si>
-    <t>reten_5 / reten_7 / reten_10 / reten_11 / reten_12 / reten_14 / reten_16 / conductor_4</t>
-  </si>
-  <si>
-    <t>reten_2 / reten_6 / reten_8 / reten_9 / reten_17 / reten_18 / reten_21 / conductor_3</t>
-  </si>
-  <si>
-    <t>reten_6 / reten_8 / reten_11 / reten_12 / reten_14 / reten_16 / reten_18 / conductor_4</t>
-  </si>
-  <si>
-    <t>reten_1 / reten_4 / reten_13 / reten_15 / reten_19 / reten_20 / reten_22 / conductor_1</t>
+    <t>diurno (08:00-20:00)</t>
+  </si>
+  <si>
+    <t>nocturno (20:00-08:00)</t>
+  </si>
+  <si>
+    <t>Reten4 / Reten5 / Reten7 / Reten9 / Reten10 / Reten11 / Reten15 / Conductor1</t>
+  </si>
+  <si>
+    <t>Reten1 / Reten2 / Reten3 / Reten8 / Reten12 / Reten17 / Reten22 / Conductor3</t>
+  </si>
+  <si>
+    <t>Reten4 / Reten5 / Reten6 / Reten13 / Reten18 / Reten19 / Reten20 / Conductor2</t>
+  </si>
+  <si>
+    <t>Reten2 / Reten8 / Reten12 / Reten14 / Reten16 / Reten17 / Reten21 / Conductor5</t>
+  </si>
+  <si>
+    <t>Reten1 / Reten3 / Reten6 / Reten18 / Reten19 / Reten20 / Reten22 / Conductor3</t>
+  </si>
+  <si>
+    <t>Reten7 / Reten9 / Reten10 / Reten11 / Reten15 / Reten16 / Reten21 / Conductor4</t>
+  </si>
+  <si>
+    <t>Reten4 / Reten5 / Reten7 / Reten9 / Reten10 / Reten11 / Reten15 / Conductor4</t>
+  </si>
+  <si>
+    <t>Reten2 / Reten8 / Reten12 / Reten14 / Reten16 / Reten17 / Reten21 / Conductor3</t>
+  </si>
+  <si>
+    <t>Reten7 / Reten9 / Reten10 / Reten11 / Reten14 / Reten15 / Reten16 / Conductor5</t>
+  </si>
+  <si>
+    <t>Reten1 / Reten3 / Reten6 / Reten13 / Reten18 / Reten20 / Reten22 / Conductor1</t>
   </si>
 </sst>
 </file>
